--- a/CleanROMs_Systems_and_Formats.xlsx
+++ b/CleanROMs_Systems_and_Formats.xlsx
@@ -13,11 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not included and why" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Supported systems'!$A$1:$E$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Supported systems'!$A$1:$E$106</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Supported systems'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ROM extensions'!$A$1:$C$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ROM extensions'!$A$1:$C$183</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'ROM extensions'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Not included and why'!$A$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Not included and why'!$A$1:$D$57</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Not included and why'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -505,7 +505,6 @@
           <t>CleanROMs — supported systems and formats</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -515,7 +514,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.8.1</t>
         </is>
       </c>
     </row>
@@ -527,7 +526,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>RetroBat_8_2_1_sistemas_extensiones_ROM.xlsx (99 system folders)</t>
+          <t>RetroBat_8_2_1_sistemas_extensiones_ROM.xlsx (99 system folders) + Diferencias_RetroBat_8_3_1_1_vs_Retrobat_8_1 (RetroBat 8.3.1.1)</t>
         </is>
       </c>
     </row>
@@ -542,7 +541,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
@@ -558,11 +557,11 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   of which NEW (RetroBat 8.2.1 table)</t>
+          <t xml:space="preserve">   of which NEW (RetroBat 8.2.1 and 8.3.1.1)</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -582,7 +581,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -598,11 +597,11 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   of which NEW</t>
+          <t xml:space="preserve">   of which NEW (RetroBat 8.2.1 and 8.3.1.1)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12">
@@ -622,7 +621,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -677,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -710,7 +709,7 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>Extensions declared by RetroBat 8.2.1</t>
+          <t>Extensions declared by RetroBat (8.2.1 / 8.3.1.1)</t>
         </is>
       </c>
     </row>
@@ -1012,29 +1011,29 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Desktop consoles</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Master System</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>mastersystem</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>.bin .sms .wad .zip .7z</t>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Sony PlayStation 4 (PS4)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ps4</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.3.1.1)</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>.ps4 .zar .m3u .lnk</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1045,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Sega Mega Drive / Genesis</t>
+          <t>Master System</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>megadrive</t>
+          <t>mastersystem</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1061,7 +1060,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>.bin .gen .md .sg .smd .32x .cue .iso .zip .7z</t>
+          <t>.bin .sms .wad .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1072,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Sega CD / Mega CD</t>
+          <t>Sega Mega Drive / Genesis</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>segacd</t>
+          <t>megadrive</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1088,7 +1087,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>.cue .iso .chd .m3u .ccd .cso .bin .zip .7z</t>
+          <t>.bin .gen .md .sg .smd .32x .cue .iso .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1099,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Sega Saturn</t>
+          <t>Sega CD / Mega CD</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>saturn</t>
+          <t>segacd</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1115,7 +1114,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>.cue .iso .chd .m3u .ccd .cso .zip .7z</t>
+          <t>.cue .iso .chd .m3u .ccd .cso .bin .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1126,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Sega Dreamcast</t>
+          <t>Sega Saturn</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>dreamcast</t>
+          <t>saturn</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1142,7 +1141,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>.cdi .gdi .chd .cue .m3u .zip .7z</t>
+          <t>.cue .iso .chd .m3u .ccd .cso .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1153,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Microsoft Xbox (Clásica)</t>
+          <t>Sega Dreamcast</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>xbox</t>
+          <t>dreamcast</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1169,7 +1168,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>.iso .xiso .cci .xbe .zip .7z</t>
+          <t>.cdi .gdi .chd .cue .m3u .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1180,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Microsoft Xbox 360</t>
+          <t>Microsoft Xbox (Clásica)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>xbox360</t>
+          <t>xbox</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1196,7 +1195,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>.iso .xex .god .cci .zip .7z</t>
+          <t>.iso .xiso .cci .xbe .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1207,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Atari 2600</t>
+          <t>Microsoft Xbox 360</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>atari2600</t>
+          <t>xbox360</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1223,7 +1222,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>.a26 .bin .rom .zip .7z</t>
+          <t>.iso .xex .god .cci .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1234,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Atari 7800</t>
+          <t>Atari 2600</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>atari7800</t>
+          <t>atari2600</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1250,7 +1249,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>.a78 .bin .rom .zip .7z</t>
+          <t>.a26 .bin .rom .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1261,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Atari Jaguar</t>
+          <t>Atari 7800</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>atarijaguar</t>
+          <t>atari7800</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1277,7 +1276,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.a78 .bin .rom .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1288,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>TurboGrafx-16 / PC Engine</t>
+          <t>Atari Jaguar</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>pcengine</t>
+          <t>atarijaguar</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1304,7 +1303,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>.pce .cue .ccd .chd .iso .zip .7z</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1315,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>ColecoVision</t>
+          <t>TurboGrafx-16 / PC Engine</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>coleco</t>
+          <t>pcengine</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1331,7 +1330,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.pce .cue .ccd .chd .iso .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1342,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Mattel Intellivision</t>
+          <t>ColecoVision</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>intellivision</t>
+          <t>coleco</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1358,7 +1357,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>.int .bin .rom .zip .7z</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1369,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>GCE Vectrex</t>
+          <t>Mattel Intellivision</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>vectrex</t>
+          <t>intellivision</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1385,7 +1384,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>.vec .bin .gam .zip .7z</t>
+          <t>.int .bin .rom .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1396,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Panasonic 3DO</t>
+          <t>GCE Vectrex</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>3do</t>
+          <t>vectrex</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1412,7 +1411,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>.iso .cue .chd .bin .zip .7z</t>
+          <t>.vec .bin .gam .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1424,49 +1423,49 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
+          <t>Panasonic 3DO</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>3do</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>.iso .cue .chd .bin .zip .7z</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Desktop consoles</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
           <t>Philips CD-i</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>cdi</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Desktop consoles</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Sega 32X</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>sega32x</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>.32x .smd .bin .md .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1477,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Atari 5200</t>
+          <t>Sega 32X</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>atari5200</t>
+          <t>sega32x</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1493,7 +1492,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>.a52 .bin .rom .zip .7z</t>
+          <t>.32x .smd .bin .md .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1504,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Magnavox Odyssey²</t>
+          <t>Atari 5200</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>odyssey2</t>
+          <t>atari5200</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1520,7 +1519,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>.bin .rom .zip .7z</t>
+          <t>.a52 .bin .rom .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1531,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Philips Videopac</t>
+          <t>Magnavox Odyssey²</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>videopac</t>
+          <t>odyssey2</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1559,12 +1558,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>NEC SuperGrafx</t>
+          <t>Philips Videopac</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>supergrafx</t>
+          <t>videopac</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1574,7 +1573,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>.pce .zip .7z</t>
+          <t>.bin .rom .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1585,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>NEC PC Engine CD / TurboGrafx-CD</t>
+          <t>NEC SuperGrafx</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>pcenginecd</t>
+          <t>supergrafx</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1601,7 +1600,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>.cue .ccd .chd .iso .m3u .zip .7z</t>
+          <t>.pce .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1612,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>SNK Neo Geo CD</t>
+          <t>NEC PC Engine CD / TurboGrafx-CD</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>neogeocd</t>
+          <t>pcenginecd</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1628,7 +1627,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>.m3u .cue .iso .cso .chd .zip .7z</t>
+          <t>.cue .ccd .chd .iso .m3u .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1639,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Pioneer LaserActive</t>
+          <t>SNK Neo Geo CD</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>laseractive</t>
+          <t>neogeocd</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1655,7 +1654,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>.mmi</t>
+          <t>.m3u .cue .iso .cso .chd .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1666,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Nintendo Virtual Boy</t>
+          <t>Pioneer LaserActive</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>virtualboy</t>
+          <t>laseractive</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1682,7 +1681,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>.vb .vboy .bin .zip .7z</t>
+          <t>.mmi</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1693,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Nintendo 64 Disk Drive (64DD)</t>
+          <t>Nintendo Virtual Boy</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>n64dd</t>
+          <t>virtualboy</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1709,7 +1708,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>.v64 .z64 .n64 .wad .zip .7z .ndd</t>
+          <t>.vb .vboy .bin .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1721,49 +1720,49 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>Nintendo 64 Disk Drive (64DD)</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>n64dd</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>.v64 .z64 .n64 .wad .zip .7z .ndd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Desktop consoles</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>Bandai SuFami Turbo</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>sufami</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>.st .fig .bs .smc .sfc .zip .7z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Handhelds</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Nintendo Game Boy (GB)</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>gb</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>.gb .gbc .dmg .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1775,12 +1774,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Nintendo Game Boy Color (GBC)</t>
+          <t>Nintendo Game Boy (GB)</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>gbc</t>
+          <t>gb</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -1802,12 +1801,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Nintendo Game Boy Advance (GBA)</t>
+          <t>Nintendo Game Boy Color (GBC)</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>gba</t>
+          <t>gbc</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -1817,7 +1816,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>.gba .agb .bin .zip .7z</t>
+          <t>.gb .gbc .dmg .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1828,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Nintendo DS (NDS)</t>
+          <t>Nintendo Game Boy Advance (GBA)</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>nds</t>
+          <t>gba</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -1844,7 +1843,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>.nds .bin .zip .7z</t>
+          <t>.gba .agb .bin .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1855,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Nintendo 3DS</t>
+          <t>Nintendo DS (NDS)</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>n3ds</t>
+          <t>nds</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -1871,7 +1870,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.nds .bin .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1883,12 +1882,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Sony PlayStation Portable (PSP)</t>
+          <t>Nintendo 3DS</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>psp</t>
+          <t>n3ds</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -1898,7 +1897,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>.iso .cso .pbp .chd .elf .prx .zip .7z</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1909,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Sony PS Vita</t>
+          <t>Sony PlayStation Portable (PSP)</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>psvita</t>
+          <t>psp</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -1925,7 +1924,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>.vpk .zip .7z</t>
+          <t>.iso .cso .pbp .chd .elf .prx .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1936,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Sega Game Gear</t>
+          <t>Sony PS Vita</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>gamegear</t>
+          <t>psvita</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -1952,7 +1951,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>.bin .gg .sms .zip .7z</t>
+          <t>.vpk .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1963,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Atari Lynx</t>
+          <t>Sega Game Gear</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>lynx</t>
+          <t>gamegear</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -1979,7 +1978,7 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.bin .gg .sms .zip .7z</t>
         </is>
       </c>
     </row>
@@ -1991,12 +1990,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>SNK Neo Geo Pocket / Color</t>
+          <t>Atari Lynx</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>ngpc</t>
+          <t>lynx</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -2006,7 +2005,7 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>.ngp .ngc .zip .7z</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2018,12 +2017,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Bandai WonderSwan / Color</t>
+          <t>SNK Neo Geo Pocket / Color</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>wonderswan</t>
+          <t>ngpc</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -2033,7 +2032,7 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>.ws .wsc .zip .7z</t>
+          <t>.ngp .ngc .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2045,76 +2044,76 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
+          <t>Bandai WonderSwan / Color</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>wonderswan</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>.ws .wsc .zip .7z</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Handhelds</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
           <t>Watara Supervision</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>supervision</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Handhelds</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>Nintendo Pokémon Mini</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>pokemini</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>.min .zip .7z</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>Home computers</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Amstrad CPC</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>amstradcpc</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>.dsk .sna .tap .cdt .voc .m3u .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2125,12 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Amstrad GX4000</t>
+          <t>Amstrad CPC</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>gx4000</t>
+          <t>amstradcpc</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2141,7 +2140,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.dsk .sna .tap .cdt .voc .m3u .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2152,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>MSX / MSX2 / MSX2+</t>
+          <t>Amstrad GX4000</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>msx</t>
+          <t>gx4000</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2168,7 +2167,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>.rom .mx1 .mx2 .dsk .cas .m3u .zip .7z</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2180,12 +2179,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Sinclair ZX Spectrum</t>
+          <t>MSX / MSX2 / MSX2+</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>zxspectrum</t>
+          <t>msx</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2195,7 +2194,7 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>.tzx .tap .z80 .sna .szx .trd .dsk .mgt .udi .zip .7z</t>
+          <t>.rom .mx1 .mx2 .dsk .cas .m3u .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2206,12 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Commodore 64 (C64)</t>
+          <t>Sinclair ZX Spectrum</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>c64</t>
+          <t>zxspectrum</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -2222,7 +2221,7 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>.d64 .g64 .t64 .tap .prg .crt .nib .m3u .zip .7z</t>
+          <t>.tzx .tap .z80 .sna .szx .trd .dsk .mgt .udi .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2233,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Commodore Amiga 500</t>
+          <t>Commodore 64 (C64)</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>amiga500</t>
+          <t>c64</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2249,7 +2248,7 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>.adf .adz .dms .ipf .lha .hdf .hdz .uae .m3u .zip .7z</t>
+          <t>.d64 .g64 .t64 .tap .prg .crt .nib .m3u .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2260,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Commodore Amiga 1200</t>
+          <t>Commodore Amiga 500</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>amiga1200</t>
+          <t>amiga500</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2288,12 +2287,12 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Atari ST</t>
+          <t>Commodore Amiga 1200</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>atarist</t>
+          <t>amiga1200</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -2303,7 +2302,7 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>.st .msa .stx .dim .ipf .m3u .zip .7z</t>
+          <t>.adf .adz .dms .ipf .lha .hdf .hdz .uae .m3u .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2315,12 +2314,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Apple II</t>
+          <t>Atari ST</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>apple2</t>
+          <t>atarist</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -2330,7 +2329,7 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>.do .po .dsk .nib .woz .2mg .zip .7z</t>
+          <t>.st .msa .stx .dim .ipf .m3u .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2341,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>PC DOS</t>
+          <t>Apple II</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>dos</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -2357,7 +2356,7 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>.zip .7z .dosz .exe .bat .com .conf</t>
+          <t>.do .po .dsk .nib .woz .2mg .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2369,12 +2368,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Sharp X68000</t>
+          <t>PC DOS</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>x68000</t>
+          <t>dos</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -2384,7 +2383,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.zip .7z .dosz .exe .bat .com .conf</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2395,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>NEC PC-9801</t>
+          <t>Sharp X68000</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>pc98</t>
+          <t>x68000</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -2423,49 +2422,49 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
+          <t>NEC PC-9801</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>pc98</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Home computers</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
           <t>Thomson MO/TO</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>thomson</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Home computers</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Apple IIGS</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>apple2gs</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>.2mg .po .dsk .hdv .woz .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2477,12 +2476,12 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Coleco Adam</t>
+          <t>Apple IIGS</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>adam</t>
+          <t>apple2gs</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2492,7 +2491,7 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>.ddp .dsk .rom .bin .zip .7z</t>
+          <t>.2mg .po .dsk .hdv .woz .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2503,12 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Commodore VIC-20</t>
+          <t>Coleco Adam</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>vic20</t>
+          <t>adam</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2519,7 +2518,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>.a0 .b0 .d0 .g0 .j0 .p0 .t0 .prg .crt .zip .7z</t>
+          <t>.ddp .dsk .rom .bin .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2530,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Sinclair ZX81</t>
+          <t>Commodore VIC-20</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>zx81</t>
+          <t>vic20</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2546,7 +2545,7 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>.p .tzx .t81 .zip .7z</t>
+          <t>.a0 .b0 .d0 .g0 .j0 .p0 .t0 .prg .crt .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2557,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Commodore Amiga CD32</t>
+          <t>Sinclair ZX81</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>amigacd32</t>
+          <t>zx81</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2573,7 +2572,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>.cue .iso .chd .ccd .img .bin .lha .zip .7z</t>
+          <t>.p .tzx .t81 .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2585,49 +2584,49 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
+          <t>Commodore Amiga CD32</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>amigacd32</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>.cue .iso .chd .ccd .img .bin .lha .zip .7z</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Home computers</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
           <t>Commodore Amiga CDTV</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>amigacdtv</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>.cue .iso .chd .ccd .img .bin .lha .zip .7z</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Arcade systems</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>Capcom Play System I (CPS1)</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>cps1</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>.fba .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2638,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Capcom Play System II (CPS2)</t>
+          <t>Capcom Play System I (CPS1)</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>cps2</t>
+          <t>cps1</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -2666,12 +2665,12 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Capcom Play System III (CPS3)</t>
+          <t>Capcom Play System II (CPS2)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>cps3</t>
+          <t>cps2</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -2693,12 +2692,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>SNK Neo-Geo AES / MVS</t>
+          <t>Capcom Play System III (CPS3)</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>neogeo</t>
+          <t>cps3</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -2708,7 +2707,7 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>.zip .wad .neo .7z</t>
+          <t>.fba .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2720,12 +2719,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>MAME (General Arcade)</t>
+          <t>SNK Neo-Geo AES / MVS</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>mame</t>
+          <t>neogeo</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -2735,7 +2734,7 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>.zip .7z .decomp</t>
+          <t>.zip .wad .neo .7z</t>
         </is>
       </c>
     </row>
@@ -2747,12 +2746,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>FinalBurn Neo (FBNeo)</t>
+          <t>MAME (General Arcade)</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>fbneo</t>
+          <t>mame</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -2762,7 +2761,7 @@
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>.fba .zip .chd .7z .bin</t>
+          <t>.zip .7z .decomp</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2773,12 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Sammy Atomiswave</t>
+          <t>FinalBurn Neo (FBNeo)</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>atomiswave</t>
+          <t>fbneo</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -2789,7 +2788,7 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>.bin .lst .zip .7z</t>
+          <t>.fba .zip .chd .7z .bin</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2800,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Sega Naomi / Naomi 2</t>
+          <t>Sammy Atomiswave</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>naomi</t>
+          <t>atomiswave</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -2816,7 +2815,7 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>.bin .dat .lst .zip .7z</t>
+          <t>.bin .lst .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2828,12 +2827,12 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Sega Model 2</t>
+          <t>Sega Naomi / Naomi 2</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>naomi</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -2843,7 +2842,7 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>.zip .decomp</t>
+          <t>.bin .dat .lst .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2855,12 +2854,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Sega Model 3</t>
+          <t>Sega Model 2</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -2882,49 +2881,49 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
+          <t>Sega Model 3</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>model3</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>.zip .decomp</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Arcade systems</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
           <t>LaserDisc (Daphne / Singe)</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>daphne</t>
         </is>
       </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>.daphne .hypseus .7z .rar .squashfs</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>Arcade systems</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>CAVE</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>cave</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>.fba .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2936,12 +2935,12 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Gaelco PowerVR</t>
+          <t>CAVE</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>gaelco</t>
+          <t>cave</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2951,7 +2950,7 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>.zip</t>
+          <t>.fba .zip .7z</t>
         </is>
       </c>
     </row>
@@ -2963,12 +2962,12 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>MAME Homebrew (HBMAME)</t>
+          <t>Gaelco PowerVR</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>hbmame</t>
+          <t>gaelco</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2978,7 +2977,7 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>.zip .hb</t>
+          <t>.zip</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2989,12 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Sega Chihiro</t>
+          <t>MAME Homebrew (HBMAME)</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>chihiro</t>
+          <t>hbmame</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -3005,7 +3004,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>.xbe .iso</t>
+          <t>.zip .hb</t>
         </is>
       </c>
     </row>
@@ -3017,12 +3016,12 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Sega Hikaru</t>
+          <t>Sega Chihiro</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>hikaru</t>
+          <t>chihiro</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -3032,7 +3031,7 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>.zip</t>
+          <t>.xbe .iso</t>
         </is>
       </c>
     </row>
@@ -3044,12 +3043,12 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Sega Naomi 2</t>
+          <t>Sega Hikaru</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>naomi2</t>
+          <t>hikaru</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -3059,7 +3058,7 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>.zip .7z</t>
+          <t>.zip</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3070,12 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Sega Naomi GD-ROM</t>
+          <t>Sega Naomi 2</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>naomigd</t>
+          <t>naomi2</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -3086,7 +3085,7 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>.cdi .gdi .chd .cue .m3u .zip .7z</t>
+          <t>.zip .7z</t>
         </is>
       </c>
     </row>
@@ -3098,12 +3097,12 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Sega Triforce</t>
+          <t>Sega Naomi GD-ROM</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>triforce</t>
+          <t>naomigd</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -3113,7 +3112,7 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>.iso .zip .cue .7z</t>
+          <t>.cdi .gdi .chd .cue .m3u .zip .7z</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3124,12 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Singe (LaserDisc)</t>
+          <t>Sega Triforce</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>singe</t>
+          <t>triforce</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -3140,7 +3139,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>.hypseus .zip</t>
+          <t>.iso .zip .cue .7z</t>
         </is>
       </c>
     </row>
@@ -3152,12 +3151,12 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>ActionMax (LaserDisc)</t>
+          <t>Singe (LaserDisc)</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>actionmax</t>
+          <t>singe</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -3167,24 +3166,24 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>.actionmax</t>
+          <t>.hypseus .zip</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>Game engines and others</t>
+          <t>Arcade systems</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>ScummVM</t>
+          <t>ActionMax (LaserDisc)</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>scummvm</t>
+          <t>actionmax</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -3194,7 +3193,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>.scummvm .svm .game .zip .7z</t>
+          <t>.actionmax</t>
         </is>
       </c>
     </row>
@@ -3206,12 +3205,12 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>LÖVE</t>
+          <t>ScummVM</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>love</t>
+          <t>scummvm</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -3221,7 +3220,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>.love</t>
+          <t>.scummvm .svm .game .zip .7z</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3232,12 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>OpenBOR</t>
+          <t>LÖVE</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>openbor</t>
+          <t>love</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -3248,7 +3247,7 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>.pak .7z .zip</t>
+          <t>.love</t>
         </is>
       </c>
     </row>
@@ -3260,12 +3259,12 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>PICO-8</t>
+          <t>OpenBOR</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>pico8</t>
+          <t>openbor</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -3275,7 +3274,7 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>.p8 .png</t>
+          <t>.pak .7z .zip</t>
         </is>
       </c>
     </row>
@@ -3287,12 +3286,12 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>TIC-80</t>
+          <t>PICO-8</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>tic80</t>
+          <t>pico8</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -3302,7 +3301,7 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>.tic</t>
+          <t>.p8 .png</t>
         </is>
       </c>
     </row>
@@ -3314,12 +3313,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Java 2 Micro Edition (J2ME)</t>
+          <t>TIC-80</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>j2me</t>
+          <t>tic80</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -3329,7 +3328,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>.jar</t>
+          <t>.tic</t>
         </is>
       </c>
     </row>
@@ -3341,49 +3340,49 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
+          <t>Java 2 Micro Edition (J2ME)</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>j2me</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>.jar</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Game engines and others</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
           <t>Adobe Flash</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>flash</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>.swf</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>Alternative folder names (RetroBat 8.x)</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Atari Jaguar (folder jaguar)</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>jaguar</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>Alternative folder name (RetroBat 8.x)</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>.j64 .jag .abs .cof .bin .zip .7z</t>
         </is>
       </c>
     </row>
@@ -3395,12 +3394,12 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>ColecoVision (folder colecovision)</t>
+          <t>Atari Jaguar (folder jaguar)</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>colecovision</t>
+          <t>jaguar</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -3410,7 +3409,7 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>.col .rom .bin .zip .7z</t>
+          <t>.j64 .jag .abs .cof .bin .zip .7z</t>
         </is>
       </c>
     </row>
@@ -3422,12 +3421,12 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Atari Lynx (folder atarilynx)</t>
+          <t>ColecoVision (folder colecovision)</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>atarilynx</t>
+          <t>colecovision</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -3437,7 +3436,7 @@
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>.lnx .lyx .o .zip .7z</t>
+          <t>.col .rom .bin .zip .7z</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3448,12 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>Nintendo 3DS (folder 3ds)</t>
+          <t>Atari Lynx (folder atarilynx)</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>3ds</t>
+          <t>atarilynx</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -3464,7 +3463,7 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>.3ds .3dsx .cia .cxi .app .cci .elf .axf .zip .7z</t>
+          <t>.lnx .lyx .o .zip .7z</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3475,12 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Amstrad GX4000 (folder amstradgx4000)</t>
+          <t>Nintendo 3DS (folder 3ds)</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>amstradgx4000</t>
+          <t>3ds</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -3491,7 +3490,7 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>.cpr .dsk .m3u .zip .7z</t>
+          <t>.3ds .3dsx .cia .cxi .app .cci .elf .axf .zip .7z</t>
         </is>
       </c>
     </row>
@@ -3503,27 +3502,54 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
+          <t>Amstrad GX4000 (folder amstradgx4000)</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>amstradgx4000</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Alternative folder name (RetroBat 8.x)</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>.cpr .dsk .m3u .zip .7z</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>Alternative folder names (RetroBat 8.x)</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
           <t>SNK Neo Geo Pocket (folder ngp)</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>ngp</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>Alternative folder name (RetroBat 8.x)</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t>.ngp .ngc .zip .7z</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E105"/>
+  <autoFilter ref="A1:E106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3535,7 +3561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C177"/>
+  <dimension ref="A1:C183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3556,7 +3582,7 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>RetroBat 8.2.1 folders that declare it</t>
+          <t>RetroBat (8.2.1 / 8.3.1.1) folders that declare it</t>
         </is>
       </c>
     </row>
@@ -3629,153 +3655,153 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>.68k</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.3.1.1)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>megadrive</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>.7z</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>sega32x, segacd, n64dd, sufami, cave, cps1, cps2, cps3, fbneo, mame, atomiswave, naomi, naomi2, naomigd, triforce, daphne, scummvm, 3do, amstradgx4000, atari2600, atari5200, atari7800, jaguar, colecovision, vectrex, odyssey2, intellivision, xbox, xbox360, pcengine, supergrafx, n64, nes, gamecube, wii, videopac, neogeo, neogeocd, dreamcast, mastersystem, megadrive, saturn, psx, ps2, ps3, snes, pcenginecd, virtualboy, openbor, amstradcpc, apple2, apple2gs, atarist, adam, c64, amiga1200, amiga500, vic20, dos, msx, pc, zxspectrum, zx81, amigacd32, amigacdtv, atarilynx, wonderswan, 3ds, nds, gb, gba, gbc, pokemini, ngp, ngpc, gamegear, psp, psvita</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>.a0</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>vic20</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>.a26</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>atari2600</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>.a52</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>atari5200</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>.a78</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>atari7800</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>.abs</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>jaguar</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
+          <t>.abs</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>jaguar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>.actionmax</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>actionmax</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>.adf</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>amiga1200, amiga500</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>.adz</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>amiga1200, amiga500</t>
         </is>
@@ -3784,7 +3810,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>.agb</t>
+          <t>.adz</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -3794,14 +3820,14 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>gba</t>
+          <t>amiga1200, amiga500</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>.axf</t>
+          <t>.agb</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -3811,99 +3837,99 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>3ds</t>
+          <t>gba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>.axf</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>3ds</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
           <t>.b0</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>vic20</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>.bin</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>sega32x, segacd, fbneo, atomiswave, naomi, 3do, atari2600, atari5200, atari7800, jaguar, colecovision, vectrex, odyssey2, intellivision, videopac, mastersystem, megadrive, psx, ps2, virtualboy, adam, amigacd32, amigacdtv, nds, gba, gamegear</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>.bs</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>sufami</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>.bs</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>sufami</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>.bsx</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>snes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>.cas</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>msx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>.cci</t>
+          <t>.cas</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -3913,14 +3939,14 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>xbox, xbox360, 3ds</t>
+          <t>msx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>.cdi</t>
+          <t>.cci</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -3930,14 +3956,14 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>naomigd, dreamcast</t>
+          <t>xbox, xbox360, 3ds</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>.cdt</t>
+          <t>.cdi</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -3947,99 +3973,99 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>amstradcpc</t>
+          <t>naomigd, dreamcast</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>.cdt</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>amstradcpc</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
           <t>.chd</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>segacd, fbneo, naomigd, 3do, pcengine, neogeocd, dreamcast, saturn, psx, ps2, pcenginecd, amigacd32, amigacdtv, psp</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>.cia</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>3ds</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>.ciso</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>gamecube, wii</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>.cof</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>jaguar</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>.col</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>colecovision</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>.cpc</t>
+          <t>.col</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -4049,14 +4075,14 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>colecovision</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>.cpr</t>
+          <t>.cpc</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -4066,14 +4092,14 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>amstradgx4000</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>.crt</t>
+          <t>.cpr</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -4083,14 +4109,14 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>c64, vic20</t>
+          <t>amstradgx4000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>.cso</t>
+          <t>.crt</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -4100,14 +4126,14 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>segacd, neogeocd, saturn, ps2, psp</t>
+          <t>c64, vic20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>.cue</t>
+          <t>.cso</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -4117,65 +4143,65 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>segacd, naomigd, triforce, 3do, pcengine, neogeocd, dreamcast, megadrive, saturn, psx, pcenginecd, pc, amigacd32, amigacdtv</t>
+          <t>segacd, neogeocd, saturn, ps2, psp</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>.cue</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>segacd, naomigd, triforce, 3do, pcengine, neogeocd, dreamcast, megadrive, saturn, psx, pcenginecd, pc, amigacd32, amigacdtv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>.cxi</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>3ds</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>.d0</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>vic20</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>.d64</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>c64</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>.d88</t>
+          <t>.d64</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -4185,14 +4211,14 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>c64</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>.d98</t>
+          <t>.d88</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -4209,211 +4235,211 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
+          <t>.d98</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
           <t>.dap</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>.daphne</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>daphne</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
+          <t>.daphne</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>daphne</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
           <t>.ddp</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>adam</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>.dim</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>atarist</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>.dmg</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>gb, gbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>.dms</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>amiga1200, amiga500</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
+          <t>.dms</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>amiga1200, amiga500</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
           <t>.do</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>apple2</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>.dol</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>gamecube, wii</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>.dosz</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>dos</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
+          <t>.dosz</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>dos</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
           <t>.dsk</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>amstradgx4000, amstradcpc, apple2, apple2gs, adam, msx, zxspectrum</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>.dx2</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>snes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>.fba</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>cave, cps1, cps2, cps3, fbneo</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>.fd</t>
+          <t>.fba</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -4423,14 +4449,14 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cave, cps1, cps2, cps3, fbneo</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>.fdi</t>
+          <t>.fd</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -4447,7 +4473,7 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>.fds</t>
+          <t>.fdi</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
@@ -4457,99 +4483,99 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>nes</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
+          <t>.fds</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>nes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
           <t>.fig</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>sufami, snes</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>.g0</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>vic20</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>.g64</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>c64</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>.gam</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>vectrex</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>.gb</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>gb, gbc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>.gba</t>
+          <t>.gb</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -4559,14 +4585,14 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>gba</t>
+          <t>gb, gbc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>.gbc</t>
+          <t>.gba</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -4576,14 +4602,14 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>gb, gbc</t>
+          <t>gba</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>.gcm</t>
+          <t>.gbc</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -4593,82 +4619,82 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>gamecube, wii</t>
+          <t>gb, gbc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
+          <t>.gcm</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>gamecube, wii</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
           <t>.gcz</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>gamecube, wii</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>.gd3</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>snes</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
+          <t>.gd3</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>snes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
           <t>.gd7</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>snes</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>.gdi</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>naomigd, dreamcast</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>.gen</t>
+          <t>.gdi</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -4678,14 +4704,14 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>megadrive</t>
+          <t>naomigd, dreamcast</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>.gg</t>
+          <t>.gen</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
@@ -4695,14 +4721,14 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>gamegear</t>
+          <t>megadrive</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>.gz</t>
+          <t>.gg</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
@@ -4712,14 +4738,14 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>ps2</t>
+          <t>gamegear</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>.hdf</t>
+          <t>.gz</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
@@ -4729,14 +4755,14 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>amiga1200, amiga500</t>
+          <t>ps2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>.hdi</t>
+          <t>.hdf</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
@@ -4746,14 +4772,14 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>amiga1200, amiga500</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>.hds</t>
+          <t>.hdi</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
@@ -4770,75 +4796,75 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
+          <t>.hds</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
           <t>.hdv</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>apple2gs</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>.hdz</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>amiga1200, amiga500</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
+          <t>.hdz</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>amiga1200, amiga500</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
           <t>.hypseus</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>daphne, singe</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>.img</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>psx, amigacd32, amigacdtv</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>.int</t>
+          <t>.img</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -4848,14 +4874,14 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>intellivision</t>
+          <t>psx, amigacd32, amigacdtv</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>.ipf</t>
+          <t>.int</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -4865,235 +4891,235 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>atarist, amiga1200, amiga500</t>
+          <t>intellivision</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
+          <t>.ipf</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>atarist, amiga1200, amiga500</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
           <t>.iso</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>segacd, chihiro, triforce, 3do, xbox, xbox360, pcengine, gamecube, wii, neogeocd, megadrive, saturn, psx, ps2, ps3, pcenginecd, pc, amigacd32, amigacdtv, psp</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>.j0</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>vic20</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>.j64</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>jaguar</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
+          <t>.j64</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>jaguar</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
           <t>.jag</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>jaguar</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>.jar</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>j2me</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>.k7</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>.kip</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>switch</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
+          <t>.kip</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
           <t>.kip1</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>switch</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>.lha</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>amiga1200, amiga500, amigacd32, amigacdtv</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
+          <t>.lha</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>amiga1200, amiga500, amigacd32, amigacdtv</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
           <t>.lnx</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>atarilynx</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>.love</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>love</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
+          <t>.love</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
           <t>.lyx</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>atarilynx</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>.m3u</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>segacd, naomigd, amstradgx4000, gamecube, wii, neogeocd, dreamcast, saturn, psx, ps2, pcenginecd, amstradcpc, atarist, c64, amiga1200, amiga500, msx</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>.m5</t>
+          <t>.m3u</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
@@ -5103,14 +5129,14 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>segacd, naomigd, amstradgx4000, gamecube, wii, neogeocd, dreamcast, saturn, psx, ps2, pcenginecd, amstradcpc, atarist, c64, amiga1200, amiga500, msx</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>.m7</t>
+          <t>.m5</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
@@ -5127,41 +5153,41 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
+          <t>.m7</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
           <t>.md</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>sega32x, megadrive</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>.mgt</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>zxspectrum</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>.min</t>
+          <t>.mgt</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
@@ -5171,48 +5197,48 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>pokemini</t>
+          <t>zxspectrum</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
+          <t>.min</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>pokemini</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
           <t>.mmi</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>laseractive</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>.msa</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>atarist</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>.mx1</t>
+          <t>.msa</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -5222,14 +5248,14 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>msx</t>
+          <t>atarist</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>.mx2</t>
+          <t>.mx1</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -5246,7 +5272,7 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>.n64</t>
+          <t>.mx2</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -5256,99 +5282,99 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>n64dd, n64</t>
+          <t>msx</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
+          <t>.n64</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>n64dd, n64</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
           <t>.nca</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>.ndd</t>
         </is>
       </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>n64dd</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>.nds</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
         <is>
           <t>nds</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>.neo</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>neogeo</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>.nes</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>nes</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>.ngc</t>
+          <t>.nes</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
@@ -5358,14 +5384,14 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>ngp, ngpc</t>
+          <t>nes</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>.ngp</t>
+          <t>.ngc</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
@@ -5382,7 +5408,7 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>.nhd</t>
+          <t>.ngp</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
@@ -5392,201 +5418,201 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ngp, ngpc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
+          <t>.nhd</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
           <t>.nib</t>
         </is>
       </c>
-      <c r="B110" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
         <is>
           <t>apple2, c64</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>.nro</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>switch</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
+          <t>.nro</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
           <t>.nso</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>switch</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>.nsp</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
         <is>
           <t>switch</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>.p0</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>vic20</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
+          <t>.p0</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>vic20</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
           <t>.p8</t>
         </is>
       </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>pico8</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>.pbp</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>psx, psp</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
+          <t>.pbp</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>psx, psp</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
           <t>.pce</t>
         </is>
       </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>pcengine, supergrafx</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>.pfs0</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>switch</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
+          <t>.pfs0</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
           <t>.pkg</t>
         </is>
       </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>ps3</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>.po</t>
-        </is>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>apple2, apple2gs</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>.prg</t>
+          <t>.po</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
@@ -5596,14 +5622,14 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>c64, vic20</t>
+          <t>apple2, apple2gs</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>.rar</t>
+          <t>.prg</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
@@ -5613,31 +5639,31 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>daphne</t>
+          <t>c64, vic20</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>.rom</t>
-        </is>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>atari2600, atari5200, atari7800, colecovision, odyssey2, intellivision, videopac, snes, adam, msx</t>
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>.ps4</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.3.1.1)</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>ps4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>.rpx</t>
+          <t>.rar</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
@@ -5647,14 +5673,14 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>wiiu</t>
+          <t>daphne</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>.rvz</t>
+          <t>.rom</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
@@ -5664,14 +5690,14 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>gamecube, wii</t>
+          <t>atari2600, atari5200, atari7800, colecovision, odyssey2, intellivision, videopac, snes, adam, msx</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>.sap</t>
+          <t>.rpx</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
@@ -5681,82 +5707,82 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>wiiu</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
+          <t>.rvz</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>gamecube, wii</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>.sap</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
           <t>.scl</t>
         </is>
       </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>.scummvm</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>scummvm</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>.self</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>ps3</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>.sfc</t>
-        </is>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>sufami, snes</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>.sg</t>
+          <t>.self</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
@@ -5766,14 +5792,14 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>megadrive</t>
+          <t>ps3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>.smc</t>
+          <t>.sfc</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -5788,43 +5814,43 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>.smd</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>sega32x, megadrive</t>
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>.sg</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>megadrive</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>.sms</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>mastersystem, gamegear</t>
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>.sgd</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.3.1.1)</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>megadrive</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>.sna</t>
+          <t>.smc</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
@@ -5834,31 +5860,31 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>amstradcpc, zxspectrum</t>
+          <t>sufami, snes</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>.squashfs</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>daphne</t>
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>.smd</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>sega32x, megadrive</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>.st</t>
+          <t>.sms</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
@@ -5868,99 +5894,99 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>sufami, atarist</t>
+          <t>mastersystem, gamegear</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
+          <t>.sna</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>amstradcpc, zxspectrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>.squashfs</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>daphne</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>.st</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>sufami, atarist</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
           <t>.stx</t>
         </is>
       </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C138" s="5" t="inlineStr">
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
         <is>
           <t>atarist</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>.sv</t>
         </is>
       </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>.svm</t>
-        </is>
-      </c>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>scummvm</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>.swc</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>snes</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>.swf</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>flash</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>.szx</t>
+          <t>.svm</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
@@ -5970,14 +5996,14 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>zxspectrum</t>
+          <t>scummvm</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>.t0</t>
+          <t>.swc</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
@@ -5987,31 +6013,31 @@
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>vic20</t>
+          <t>snes</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>.t64</t>
-        </is>
-      </c>
-      <c r="B145" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>c64</t>
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>.swf</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>flash</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>.t81</t>
+          <t>.szx</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
@@ -6021,31 +6047,31 @@
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>zx81</t>
+          <t>zxspectrum</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="inlineStr">
-        <is>
-          <t>.tap</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>amstradcpc, c64, zxspectrum</t>
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>.t0</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>vic20</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>.thd</t>
+          <t>.t64</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -6055,14 +6081,14 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>c64</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>.tic</t>
+          <t>.t81</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
@@ -6072,14 +6098,14 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>tic80</t>
+          <t>zx81</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>.trd</t>
+          <t>.tap</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
@@ -6089,14 +6115,14 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>zxspectrum</t>
+          <t>amstradcpc, c64, zxspectrum</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>.tzx</t>
+          <t>.thd</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
@@ -6106,14 +6132,14 @@
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>zxspectrum, zx81</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>.udi</t>
+          <t>.tic</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
@@ -6123,14 +6149,14 @@
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>zxspectrum</t>
+          <t>tic80</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>.unf</t>
+          <t>.trd</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
@@ -6140,14 +6166,14 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zxspectrum</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>.v64</t>
+          <t>.tzx</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
@@ -6157,14 +6183,14 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>n64dd, n64</t>
+          <t>zxspectrum, zx81</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>.vb</t>
+          <t>.udi</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
@@ -6174,31 +6200,31 @@
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>virtualboy</t>
+          <t>zxspectrum</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="6" t="inlineStr">
-        <is>
-          <t>.vboy</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>virtualboy</t>
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>.unf</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>.vec</t>
+          <t>.v64</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
@@ -6208,48 +6234,48 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>vectrex</t>
+          <t>n64dd, n64</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>.voc</t>
-        </is>
-      </c>
-      <c r="B158" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C158" s="5" t="inlineStr">
-        <is>
-          <t>amstradcpc</t>
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>.vb</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>virtualboy</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>.vpk</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>psvita</t>
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>.vboy</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>virtualboy</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>.wav</t>
+          <t>.vec</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
@@ -6259,14 +6285,14 @@
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>vectrex</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>.wbfs</t>
+          <t>.voc</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
@@ -6276,116 +6302,116 @@
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>gamecube, wii</t>
+          <t>amstradcpc</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>.wia</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>gamecube, wii</t>
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>.vpk</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>psvita</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>.woz</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>apple2, apple2gs</t>
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>.wav</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
+          <t>.wbfs</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>gamecube, wii</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>.wia</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>gamecube, wii</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>.woz</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>apple2, apple2gs</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
           <t>.ws</t>
         </is>
       </c>
-      <c r="B164" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C164" s="5" t="inlineStr">
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
         <is>
           <t>wonderswan</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>.wsc</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C165" s="5" t="inlineStr">
-        <is>
-          <t>wonderswan</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t>.wua</t>
-        </is>
-      </c>
-      <c r="B166" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C166" s="5" t="inlineStr">
-        <is>
-          <t>wiiu</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>.wud</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>wiiu</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>.wux</t>
+          <t>.wsc</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
@@ -6395,14 +6421,14 @@
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>wiiu</t>
+          <t>wonderswan</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
         <is>
-          <t>.xbe</t>
+          <t>.wua</t>
         </is>
       </c>
       <c r="B169" s="5" t="inlineStr">
@@ -6412,48 +6438,48 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>chihiro, xbox</t>
+          <t>wiiu</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="inlineStr">
-        <is>
-          <t>.xci</t>
-        </is>
-      </c>
-      <c r="B170" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C170" s="5" t="inlineStr">
-        <is>
-          <t>switch</t>
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>.wud</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>wiiu</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="6" t="inlineStr">
-        <is>
-          <t>.xcz</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>switch</t>
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>.wux</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>wiiu</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>.xex</t>
+          <t>.xbe</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
@@ -6463,97 +6489,199 @@
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>xbox360</t>
+          <t>chihiro, xbox</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>.xiso</t>
+          <t>.xbox360</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
+          <t>NEW (RetroBat 8.3.1.1)</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>xbox</t>
+          <t>xbox360</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
+          <t>.xci</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>.xcp</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.3.1.1)</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>xbox360</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>.xcz</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>.xex</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>xbox360</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>.xiso</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>xbox</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
           <t>.z64</t>
         </is>
       </c>
-      <c r="B174" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C174" s="5" t="inlineStr">
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
         <is>
           <t>n64dd, n64</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="5" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
         <is>
           <t>.z80</t>
         </is>
       </c>
-      <c r="B175" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C175" s="5" t="inlineStr">
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
         <is>
           <t>zxspectrum</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="5" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>.zar</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.3.1.1)</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>ps4, xbox360</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
         <is>
           <t>.zip</t>
         </is>
       </c>
-      <c r="B176" s="5" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-      <c r="C176" s="5" t="inlineStr">
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
         <is>
           <t>sega32x, segacd, n64dd, sufami, cave, cps1, cps2, cps3, fbneo, gaelco, mame, hbmame, atomiswave, hikaru, model2, model3, naomi, naomi2, naomigd, triforce, singe, scummvm, 3do, amstradgx4000, atari2600, atari5200, atari7800, jaguar, colecovision, vectrex, odyssey2, intellivision, xbox, xbox360, pcengine, supergrafx, n64, nes, gamecube, wii, videopac, neogeo, neogeocd, dreamcast, mastersystem, megadrive, saturn, snes, pcenginecd, virtualboy, openbor, amstradcpc, apple2, apple2gs, atarist, adam, c64, amiga1200, amiga500, vic20, dos, msx, pc, zxspectrum, zx81, amigacd32, amigacdtv, atarilynx, wonderswan, 3ds, nds, gb, gba, gbc, pokemini, ngp, ngpc, gamegear, psp, psvita</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="6" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
         <is>
           <t>.zso</t>
         </is>
       </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>NEW (RetroBat 8.2.1 table)</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>NEW (RetroBat 8.2.1 table)</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
         <is>
           <t>ps2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C177"/>
+  <autoFilter ref="A1:C183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -6565,7 +6693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7740,8 +7868,96 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>.mds</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>dreamcast, saturn</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Companion file or descriptor of another one (two-file disc image): the program groups .cue/.gdi/.m3u but not this format, so it would give false 'duplicates'. Their media ARE protected so they are not moved as orphans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>.mdf</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>psx, ps2, dreamcast</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Companion file or descriptor of another one (two-file disc image): the program groups .cue/.gdi/.m3u but not this format, so it would give false 'duplicates'. Their media ARE protected so they are not moved as orphans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>.toc</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>psx, saturn</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Companion file or descriptor of another one (two-file disc image): the program groups .cue/.gdi/.m3u but not this format, so it would give false 'duplicates'. Their media ARE protected so they are not moved as orphans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>.cbn</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>psx</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Auxiliary PlayStation 1 format with no grouping logic in the program (unverified); it could give false 'duplicates'. Its media ARE protected.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D53"/>
+  <autoFilter ref="A1:D57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
